--- a/KS_folding_tests/synthetic/features_importance_synthetic.xlsx
+++ b/KS_folding_tests/synthetic/features_importance_synthetic.xlsx
@@ -705,12 +705,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>F6</t>
+          <t>F2</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>F6</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F3</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F6</t>
         </is>
       </c>
     </row>
@@ -871,17 +871,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>background5</t>
+          <t>background6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>background5</t>
+          <t>background3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>background3</t>
+          <t>background4</t>
         </is>
       </c>
     </row>
@@ -928,17 +928,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>background1</t>
+          <t>background3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>background1</t>
+          <t>background5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>background5</t>
+          <t>background6</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>background3</t>
+          <t>background5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>background3</t>
+          <t>background4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1047,12 +1047,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>background4</t>
+          <t>background1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>background4</t>
+          <t>background5</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F6</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>F6</t>
+          <t>F2</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>F6</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>F2</t>
+          <t>F3</t>
         </is>
       </c>
     </row>
@@ -1465,7 +1465,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>F3</t>
+          <t>F6</t>
         </is>
       </c>
     </row>
@@ -1512,17 +1512,17 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>background5</t>
+          <t>background6</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>background5</t>
+          <t>background3</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>background3</t>
+          <t>background4</t>
         </is>
       </c>
     </row>
@@ -1569,17 +1569,17 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>background1</t>
+          <t>background3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>background1</t>
+          <t>background5</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>background5</t>
+          <t>background6</t>
         </is>
       </c>
     </row>
@@ -1626,12 +1626,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>background3</t>
+          <t>background5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>background3</t>
+          <t>background4</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>background4</t>
+          <t>background1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>background4</t>
+          <t>background5</t>
         </is>
       </c>
     </row>
